--- a/ComplexQuestions.xlsx
+++ b/ComplexQuestions.xlsx
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H112"/>
+  <dimension ref="A1:H126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5282,6 +5282,594 @@
       <c r="H112" s="2" t="inlineStr">
         <is>
           <t>$100k CoC threshold; $95k is under. Failure = requiring CoC at $95k.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>CQ-112</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Per-lender enumeration</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>PRICING</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>I want to finance a petrol or diesel passenger vehicle. What is the lowest displayed interest rate from each lender?</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>BFS 7.60% (commercial Ultra Prime, flat across new/demo and used 2017-2026). Resimac 7.64% (PremiumPLUS motor vehicle &lt;3 years). Westpac 7.75% (Xpress dealer car up to 5 years, 24/36/48 months). Angle 7.79% (headline profile: 8+ yr ABN, 4+ yr GST, property backed, new primary asset). Metro 8.20% (passenger/commercial &lt;12t GVM, &gt;$20k, dealer). flexicommercial: NOT fundable at all -- passenger cars and SUVs are excluded outright. CFAL: no public rate card exists; pricing must come from the CFAL Credit Manager. Because the question says petrol or diesel, no EV rate or EV discount should appear in the answer.</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>bfs_commercial_rates, resimac_interest_rates, westpac_xpress_rates, angle_interest_rates, metro_interest_rates, flexi_exclusions, cfal_drivexpress_policy</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Must enumerate ALL seven, not pick a winner. Two traps: quoting EV rates/discounts when the question says petrol or diesel, and giving Flexi a rate instead of excluding it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>CQ-113</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Per-lender enumeration</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>PRICING</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>I want to finance an electric passenger vehicle. What is the lowest displayed interest rate from each lender?</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Westpac 6.75% (Xpress dealer car 7.75% less the 1% EV discount). Metro 7.20% (passenger/commercial &lt;12t &gt;$20k dealer 8.20% less the 1% MetroEco discount). Resimac 7.54% (EV row, PremiumPLUS; 7.79% other tiers) and EVs also get Green Goods terms to 84 months. BFS 7.60% -- Ultra Prime base, with NO EV-specific discount; inventing one is the failure. Angle: no EV-specific rate exists, so it prices off its normal profile table. flexicommercial: still not fundable -- the passenger car/SUV exclusion is absolute and being electric does not create a pathway. CFAL: no public rate card.</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>westpac_xpress_rates, metro_interest_rates, metro_eco, resimac_interest_rates, bfs_commercial_rates, angle_interest_rates, flexi_exclusions, cfal_drivexpress_policy</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Inverse of CQ-112: here the EV discounts MUST be applied. Failure = withholding them, or inventing an EV discount for BFS/Angle where none exists, or letting Flexi in because it is an EV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>CQ-114</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Policy-interaction edge case</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>BFS</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ELIGIBILITY</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>A BFS commercial applicant has an Experian CCR score of exactly 600. Another has 599. What changes between them?</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>600 meets the Tier 2 minimum, so that applicant is Tier 2 with full product access and no mandatory tier deposit. 599 falls short of Tier 2 and lands in Tier 3 (minimum 550), which carries a mandatory 20% deposit on EVERY application -- consumer and commercial, new and used alike, not conditional on contract type. Tier 3 can still do commercial used vehicles; that restriction only starts at Tier 4.</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>bfs_customer_tiers</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Boundary handling: 600 is the Tier 2 minimum so it QUALIFIES rather than falling short. Second trap: treating the Tier 3 deposit as conditional on contract type when it applies to every application.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>CQ-115</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Policy-interaction edge case</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>BFS</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ELIGIBILITY</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>A BFS consumer applicant has net monthly income of exactly $2,318. Is that an automatic decline?</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>No. The auto-decline triggers when consumer net monthly income is BELOW $2,318. At exactly $2,318 the applicant meets the floor and this trigger does not fire. The other auto-decline triggers still apply independently (all guarantors CCR &lt;400, &lt;550 for commercial used, or current bankruptcy).</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>bfs_customer_tiers, bfs_exclusions</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Mirror of CQ-092, where $2,200 IS a decline. A model that has learned '$2,318 -&gt; auto-decline' as an association rather than as a threshold will wrongly decline an applicant who exactly meets it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>CQ-116</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Calculation / arithmetic</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Resimac</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>PRICING</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Resimac deal: a PremiumPLUS client buying a classic car, 5 years old, through a private sale. What's the all-in rate?</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Base: classic cars sit under motor vehicles, and at 5 years old that is the '&gt;3 years' row = 8.24% read directly from the PremiumPLUS column. Risk loadings are +2% each and they stack: classic car +2% and private sale +2% = +4%, which sits exactly ON the 4%-per-deal cap, not over it, so nothing needs trimming. All-in 12.24% p.a. Brokerage loading is separate and excluded from the 4% cap. Worth adding: classic cars are excluded from balloon payments, so the balloon must be 0.</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>resimac_interest_rates, resimac_asset_categories</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Three traps: applying only one loading when the policy says multiple may apply; treating 4% as exceeding the cap when it exactly meets it; and computing PremiumPLUS by subtracting 0.25% from the Premium column instead of reading the PremiumPLUS column directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>CQ-117</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Multi-filter (single lender)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Flexi</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>PRICING</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>A company with a 3-year-old ABN and GST registration, asset backed, wants $200,000 for a primary asset. What's flexicommercial's rate?</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>7.85% p.a. ex brokerage -- the standard card's $150,001+ Primary rate. They do NOT get flexipremium's 7.15%: flexipremium requires 4+ years ABN and GST for asset-backed customers (8+ years if non-asset-backed), and this client has only 3 years. They do clear the standard matrix's 2-year minimum, so standard pricing applies rather than a decline.</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>flexi_flexipremium, flexi_standard_rates</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Inverse of the usual trap. The documented failure is quoting the standard rate when the client qualifies for premium -- so a model that over-corrects will wrongly hand out 7.15% here. Tier eligibility has to be checked in both directions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>CQ-118</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Calculation / arithmetic</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Flexi</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>PRICING</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>flexicommercial, non-asset-backed customer, $80,000 primary asset, private sale, 72-month term. Build up the rate.</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Base 8.35% ($20,001-$150,000 Primary band). Add-ons, each triggering independently: private sale +1.00%, term over 60 months +1.25%, non-asset-backed +1.50%. All-in 8.35% + 3.75% = 12.10% ex brokerage. Two conditions worth flagging: a 72-month term is only available on a Primary asset up to 3 years old (otherwise max term is 5 years), and this customer cannot reach flexipremium at all since non-asset-backed requires 8+ years ABN/GST.</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>flexi_standard_rates, flexi_flexipremium</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Three independent add-ons stacking; dropping any one yields a plausible wrong number. Also: using the $150,001+ band (7.85%) for an $80k deal, and quoting the superseded 1.25% non-asset-backed add-on instead of the current 1.50%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>CQ-119</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Contradiction detection</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Metro</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>SPECIAL_PROGRAMS</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>What's the maximum vehicle price for Metro's MetroEco electric vehicle discount?</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Metro's own documents disagree and the correct answer surfaces both rather than picking one: the rate sheet states $91,661 while the separate MetroEco product booklet states $91,387. The booklet is otherwise unchanged from its prior version, so this is a genuine cross-document conflict rather than one superseding the other. Flag both figures and confirm the current cap with Metro directly.</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>metro_interest_rates, metro_eco</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Silently picking one figure -- or averaging/reconciling them -- looks confident and is wrong. Mirrors the Angle Start-Up 500 vs 550 conflict in CQ-034, so it also tests whether that behaviour generalises.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>CQ-120</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Best-fit recommendation</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ELIGIBILITY</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>My client is a carpenter who registered his ABN and GST last week. He wants to finance a ute. Which lender can he use, and on what conditions?</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>BFS, via New Business Ventures, which explicitly covers businesses with LESS than 12 months ABN -- one week qualifies. Conditions: maximum $100,000 total exposure, 90-day bank statements (plus a run contract for couriers), a 20% deposit if the applicant is Tier 3 or Tier 4, and the ute must be a motor vehicle under 4.5T GVM. Angle must be ruled OUT despite having a Start-Up product: it requires the business to have been operating and actively trading a minimum of 3 months, and the ABN was registered last week. CFAL, flexicommercial, Metro, Resimac and Westpac all need 1-2+ years of ABN/GST history.</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>bfs_commercial_documentation, bfs_customer_tiers, bfs_vehicle_types, angle_start_up, cfal_eligibility, flexi_flexipremium, metro_passenger_vehicle_streamlined, resimac_customer_tiers, westpac_medical</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Threshold trap that cuts in opposite directions: 'last week' PASSES BFS's &lt;12-month ABN rule but FAILS Angle's 3-month trading rule. Confirmed failure mode -- recommending Angle (which the client is ineligible for) while dismissing BFS (which fits) by quoting BFS's own qualifying rule and then concluding the opposite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>CQ-121</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Policy-interaction edge case</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Westpac</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>SPECIAL_PROGRAMS</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>A physiotherapist with 5 years' experience wants $200,000 of new medical equipment under Westpac Medical. Does it fit?</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>No. A physiotherapist is an Allied Health Practitioner, and Allied Health has a SINGLE combined cap of under $150,000 spanning motor vehicle, office equipment and medical equipment -- there is no separate, higher medical-equipment limit for them. $200,000 exceeds it. Their maximum cumulative approvals are under $250,000. The under-$350,000 medical-equipment figure applies only to Medical Specialist / GP / Dental / Vet, a different category with an under-$500,000 cumulative cap. The 5 years' experience is not the blocker -- it satisfies the &gt;3-year requirement that applies to both categories.</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>westpac_medical</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>The $350k figure sits in the same table and is easy to grab. The distinction is professional CATEGORY, not asset type. The experience detail is a deliberate red herring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>CQ-122</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Contradiction detection</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Metro</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LOAN_LIMITS</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>A Metro customer with 12 months of good repayment history wants a single $400,000 truck. Their maximum exposure is $500,000 — so this fits, right?</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>No -- the premise conflates two different ceilings. Under the Trucks/Trailers streamlined product a customer with 12 months' good history has a maximum LOAN SIZE of $300,000 (dealer sale), so a single $400,000 truck exceeds it even though their aggregate EXPOSURE limit of $500,000 is higher. A deal must clear both the per-transaction cap and the aggregate cap. Also note prime movers are excluded from this streamlined product and private-sale transactions cap at $250,000.</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>metro_trucks_trailers_streamlined</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>False premise stated confidently by the broker, using a real figure. Loan-size and exposure limits sit in adjacent columns of the same table and are routinely conflated; the failure is answering 'yes' off the larger number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>CQ-123</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Negative / trap constraint</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Flexi</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ASSET_ELIGIBILITY</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>My client wants flexicommercial to fund a passenger car for their business. They can put down a 50% deposit and they've been trading 10 years. Does that get it over the line?</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>No. flexicommercial does not fund passenger cars or SUVs at all -- this is a hard asset exclusion, not a credit condition. A larger deposit, longer trading history or a stronger profile cannot satisfy it, because none of those change what the asset is. Commercial vehicles such as utes, vans and 4WDs ARE fundable as primary assets, so the alternative is a different asset, or a different lender.</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>flexi_exclusions, flexi_asset_categories</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Loaded with genuinely strong mitigants to invite a 'yes, with conditions'. Tests the hard-exclusion vs soft-condition distinction: an exclusion that rules a lender out entirely cannot be bought out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>CQ-124</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Contradiction detection</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>CFAL</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>What are CFAL's Low Doc requirements for a $150,000 transaction?</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>The premise is false: CFAL has NO Low Doc option at all. Its documentation requirements scale with transaction size instead. A $150,000 deal sits in the &lt;=$250k band, requiring client information, a BRIEF background of the business/directors, ABN for 2 years plus GST registration, full description of goods, reason for purchase, a signed privacy form from all individuals, last 2 years' financial statements and tax returns, a current asset &amp; liability statement for all directors/guarantors, and a commitment schedule. All financial statements must be no more than 18 months old.</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>cfal_documentation_matrix</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Assuming documentation tiers are standardised across the panel because most lenders have some Low/Full Doc structure. The right move is to reject the premise, not to describe CFAL's smallest-transaction requirements as though they were 'Low Doc'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>CQ-125</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Cross-lender comparison (2)</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>BFS, CFAL</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>ELIGIBILITY</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>My client is in a Remote area (ABS classification) and is non-asset-backed. What deposit will BFS want, and what about CFAL?</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>BFS: under PRIME, non-asset-backed applicants in remote areas require a 20% deposit. Two carve-outs belong in a complete answer: 'Very Remote' areas are unavailable across ALL tiers, and BFS Plus is excluded from remote-area lending entirely with no deposit-based workaround. CFAL: no such rule exists. A Remote/Very Remote restriction previously appeared in CFAL's material but was verified as belonging to Resimac's and BFS's product guides, not CFAL's, and was removed -- so there is no CFAL geography-based deposit or exclusion to apply, and CFAL is assessed on its normal criteria (2+ years ABN, current GST registration).</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>bfs_exclusions, bfs_vehicle_types, cfal_exclusions, cfal_eligibility</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Cross-lender contamination of a rule that genuinely exists at one lender and genuinely does not at another. The correct answer requires saying 'this does not apply to CFAL' rather than reaching for the nearest similar-sounding policy.</t>
         </is>
       </c>
     </row>
